--- a/03_Outputs/Consolidada_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Consolidada_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -406,7 +406,7 @@
         <v>22</v>
       </c>
       <c r="D2">
-        <v>5.523024430475022E-17</v>
+        <v>5.521545972967087E-17</v>
       </c>
       <c r="E2">
         <v>0.9999999999999999</v>
@@ -433,7 +433,7 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>2.459167654864849E-18</v>
+        <v>2.491200900870102E-18</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -460,7 +460,7 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>1.148071536828287E-16</v>
+        <v>1.147825127243631E-16</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -487,7 +487,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>-8.636902351770322E-17</v>
+        <v>-8.635916713431698E-17</v>
       </c>
       <c r="E5">
         <v>0.9999999999999999</v>
@@ -514,7 +514,7 @@
         <v>22</v>
       </c>
       <c r="D6">
-        <v>1.413405377585649E-17</v>
+        <v>1.41685511177083E-17</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -541,7 +541,7 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>3.716349355778722E-17</v>
+        <v>3.722139981018134E-17</v>
       </c>
       <c r="E7">
         <v>0.9999999999999999</v>
@@ -568,7 +568,7 @@
         <v>22</v>
       </c>
       <c r="D8">
-        <v>1.513447668955902E-17</v>
+        <v>1.513694078540558E-17</v>
       </c>
       <c r="E8">
         <v>0.9999999999999999</v>
@@ -595,7 +595,7 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>2.378776527870895E-18</v>
+        <v>2.387092851353028E-18</v>
       </c>
       <c r="E9">
         <v>0.9999999999999999</v>
@@ -622,7 +622,7 @@
         <v>22</v>
       </c>
       <c r="D10">
-        <v>1.400019176899222E-16</v>
+        <v>1.400160862410399E-16</v>
       </c>
       <c r="E10">
         <v>0.9999999999999999</v>
@@ -649,7 +649,7 @@
         <v>22</v>
       </c>
       <c r="D11">
-        <v>4.749791153825132E-17</v>
+        <v>4.752748068841002E-17</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -676,7 +676,7 @@
         <v>22</v>
       </c>
       <c r="D12">
-        <v>8.573575088513782E-17</v>
+        <v>8.57603918436034E-17</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -703,7 +703,7 @@
         <v>22</v>
       </c>
       <c r="D13">
-        <v>2.898269534721478E-17</v>
+        <v>2.899008763475445E-17</v>
       </c>
       <c r="E13">
         <v>0.9999999999999999</v>
@@ -730,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="D14">
-        <v>1.064489405713041E-17</v>
+        <v>1.066368278796041E-17</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -757,7 +757,7 @@
         <v>22</v>
       </c>
       <c r="D15">
-        <v>-1.448980761370329E-17</v>
+        <v>-1.449011562568411E-17</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>-1.731766560960938E-16</v>
+        <v>-1.731618715210144E-16</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>22</v>
       </c>
       <c r="D19">
-        <v>-1.07040323574478E-17</v>
+        <v>-1.073360150760649E-17</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -892,7 +892,7 @@
         <v>22</v>
       </c>
       <c r="D20">
-        <v>-2.858351182007239E-18</v>
+        <v>-2.846646726736088E-18</v>
       </c>
       <c r="E20">
         <v>0.9999999999999999</v>
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D21">
-        <v>-1.2021830816187E-16</v>
+        <v>-1.202238523775247E-16</v>
       </c>
       <c r="E21">
         <v>0.9999999999999999</v>
@@ -973,7 +973,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>1.548191420392369E-17</v>
+        <v>1.551148335408239E-17</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1000,7 +1000,7 @@
         <v>22</v>
       </c>
       <c r="D24">
-        <v>3.802099891238939E-17</v>
+        <v>3.803085529577562E-17</v>
       </c>
       <c r="E24">
         <v>0.9999999999999999</v>
@@ -1027,7 +1027,7 @@
         <v>22</v>
       </c>
       <c r="D25">
-        <v>-3.244721410747528E-17</v>
+        <v>-3.245275832313003E-17</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>22</v>
       </c>
       <c r="D26">
-        <v>2.455717920679668E-17</v>
+        <v>2.460646112372784E-17</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -1108,7 +1108,7 @@
         <v>22</v>
       </c>
       <c r="D28">
-        <v>-1.143340472802896E-17</v>
+        <v>-1.143586882387551E-17</v>
       </c>
       <c r="E28">
         <v>0.9999999999999999</v>
@@ -1135,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="D29">
-        <v>2.056041574367966E-17</v>
+        <v>2.057027212706589E-17</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>22</v>
       </c>
       <c r="D30">
-        <v>5.078501539755965E-17</v>
+        <v>5.079487178094588E-17</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -1189,7 +1189,7 @@
         <v>22</v>
       </c>
       <c r="D31">
-        <v>2.848494798621007E-18</v>
+        <v>2.855887086160681E-18</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -1216,7 +1216,7 @@
         <v>22</v>
       </c>
       <c r="D32">
-        <v>9.904926074409051E-17</v>
+        <v>9.903201207316459E-17</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -1243,7 +1243,7 @@
         <v>22</v>
       </c>
       <c r="D33">
-        <v>4.918828128899009E-17</v>
+        <v>4.918396912125861E-17</v>
       </c>
       <c r="E33">
         <v>1</v>

--- a/03_Outputs/Consolidada_ref_subset/04_Cluster/Summary_Stats.xlsx
+++ b/03_Outputs/Consolidada_ref_subset/04_Cluster/Summary_Stats.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>5.521545972967087E-17</v>
+        <v>-1.027410630117216E-17</v>
       </c>
       <c r="E2">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>-2.425997880485935</v>
+        <v>-2.778275040621081</v>
       </c>
       <c r="G2">
-        <v>1.192267133162734</v>
+        <v>1.250241981107736</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>2.491200900870102E-18</v>
+        <v>5.086973335952226E-17</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>-1.464746934498695</v>
+        <v>-1.586848953976759</v>
       </c>
       <c r="G3">
-        <v>2.516330631057626</v>
+        <v>1.668061299642857</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>1.147825127243631E-16</v>
+        <v>-9.051022993258752E-17</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>-1.885484094023963</v>
+        <v>-1.828876386835481</v>
       </c>
       <c r="G4">
-        <v>1.671610470368253</v>
+        <v>1.655709720112855</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>-8.635916713431698E-17</v>
+        <v>-7.664276785974911E-17</v>
       </c>
       <c r="E5">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>-2.245325559812697</v>
+        <v>-2.356808751783821</v>
       </c>
       <c r="G5">
-        <v>2.088354401300649</v>
+        <v>2.068388869367446</v>
       </c>
     </row>
     <row r="6">
@@ -511,19 +511,19 @@
         </is>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>1.41685511177083E-17</v>
+        <v>-2.081668171172169E-17</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F6">
-        <v>-1.429764574405501</v>
+        <v>-1.421764030644861</v>
       </c>
       <c r="G6">
-        <v>2.375705545758349</v>
+        <v>2.309138852327837</v>
       </c>
     </row>
     <row r="7">
@@ -538,19 +538,19 @@
         </is>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>3.722139981018134E-17</v>
+        <v>1.991253454288109E-18</v>
       </c>
       <c r="E7">
         <v>0.9999999999999999</v>
       </c>
       <c r="F7">
-        <v>-1.901699202863841</v>
+        <v>-1.844339423329817</v>
       </c>
       <c r="G7">
-        <v>2.171385795354605</v>
+        <v>2.15006730475362</v>
       </c>
     </row>
     <row r="8">
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>1.513694078540558E-17</v>
+        <v>6.555292849546881E-17</v>
       </c>
       <c r="E8">
         <v>0.9999999999999999</v>
       </c>
       <c r="F8">
-        <v>-1.614588356844653</v>
+        <v>-1.678782683594236</v>
       </c>
       <c r="G8">
-        <v>2.931052031813679</v>
+        <v>2.89858178074762</v>
       </c>
     </row>
     <row r="9">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>2.387092851353028E-18</v>
+        <v>6.228999624303624E-18</v>
       </c>
       <c r="E9">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>-0.5109403817858121</v>
+        <v>-0.4979483687051484</v>
       </c>
       <c r="G9">
-        <v>4.41506087174547</v>
+        <v>4.30936236824475</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="C10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>1.400160862410399E-16</v>
+        <v>-1.440556193677794E-16</v>
       </c>
       <c r="E10">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>-2.299034376137604</v>
+        <v>-2.280488420504854</v>
       </c>
       <c r="G10">
-        <v>1.954527599536878</v>
+        <v>1.896043317050826</v>
       </c>
     </row>
     <row r="11">
@@ -646,19 +646,19 @@
         </is>
       </c>
       <c r="C11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>4.752748068841002E-17</v>
+        <v>7.73707321755608E-17</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>-1.656799540306184</v>
+        <v>-1.767921698315221</v>
       </c>
       <c r="G11">
-        <v>1.532466053843609</v>
+        <v>1.504979623795812</v>
       </c>
     </row>
     <row r="12">
@@ -673,19 +673,19 @@
         </is>
       </c>
       <c r="C12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12">
-        <v>8.57603918436034E-17</v>
+        <v>7.733459210314463E-17</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>-1.248259406014539</v>
+        <v>-1.207503318554842</v>
       </c>
       <c r="G12">
-        <v>2.329263374587369</v>
+        <v>2.290690159531279</v>
       </c>
     </row>
     <row r="13">
@@ -700,19 +700,19 @@
         </is>
       </c>
       <c r="C13">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>2.899008763475445E-17</v>
+        <v>4.13235913741618E-17</v>
       </c>
       <c r="E13">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>-1.619918890964007</v>
+        <v>-1.582437363555727</v>
       </c>
       <c r="G13">
-        <v>1.852831475537607</v>
+        <v>1.806709982334541</v>
       </c>
     </row>
     <row r="14">
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D14">
-        <v>1.066368278796041E-17</v>
+        <v>-7.993409588336583E-17</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F14">
-        <v>-2.2190116646</v>
+        <v>-2.155602660519211</v>
       </c>
       <c r="G14">
-        <v>1.322996042481685</v>
+        <v>1.314244456509997</v>
       </c>
     </row>
     <row r="15">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15">
-        <v>-1.449011562568411E-17</v>
+        <v>-3.32488666228888E-18</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>-1.570485058396011</v>
+        <v>-1.555526465470993</v>
       </c>
       <c r="G15">
-        <v>1.529252408826315</v>
+        <v>1.480172475165824</v>
       </c>
     </row>
     <row r="16">
@@ -781,19 +781,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16">
-        <v>-1.731618715210144E-16</v>
+        <v>5.798158332427837E-17</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>-2.569433624248875</v>
+        <v>-2.51180977466462</v>
       </c>
       <c r="G16">
-        <v>1.634950484073729</v>
+        <v>1.591957362585998</v>
       </c>
     </row>
     <row r="17">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>-3.469446951953614E-18</v>
+        <v>-2.340844119071084E-17</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>-1.546502805907696</v>
+        <v>-1.64127679495696</v>
       </c>
       <c r="G17">
-        <v>2.319453847263542</v>
+        <v>2.303002660094195</v>
       </c>
     </row>
     <row r="18">
@@ -835,19 +835,19 @@
         </is>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>-1.83560355993489E-16</v>
+        <v>1.781240912043923E-16</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F18">
-        <v>-2.538484034943318</v>
+        <v>-2.527063944910875</v>
       </c>
       <c r="G18">
-        <v>1.310343375486137</v>
+        <v>1.380854409901133</v>
       </c>
     </row>
     <row r="19">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="C19">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19">
-        <v>-1.073360150760649E-17</v>
+        <v>-3.985733700756235E-18</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>-2.427059471236581</v>
+        <v>-2.38769700720543</v>
       </c>
       <c r="G19">
-        <v>1.568984861916798</v>
+        <v>1.520700142886092</v>
       </c>
     </row>
     <row r="20">
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D20">
-        <v>-2.846646726736088E-18</v>
+        <v>-2.446231151670419E-17</v>
       </c>
       <c r="E20">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>-2.269908414444482</v>
+        <v>-2.20726602826855</v>
       </c>
       <c r="G20">
-        <v>1.515216881226998</v>
+        <v>1.52045731713945</v>
       </c>
     </row>
     <row r="21">
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D21">
-        <v>-1.202238523775247E-16</v>
+        <v>-1.044189949453301E-16</v>
       </c>
       <c r="E21">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>-1.738285918071532</v>
+        <v>-1.883184705231597</v>
       </c>
       <c r="G21">
-        <v>2.07396025737248</v>
+        <v>2.079493315086005</v>
       </c>
     </row>
     <row r="22">
@@ -943,19 +943,19 @@
         </is>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22">
-        <v>2.298508605669269E-17</v>
+        <v>-1.734723475976807E-17</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F22">
-        <v>-1.923543425410126</v>
+        <v>-1.865651756693691</v>
       </c>
       <c r="G22">
-        <v>2.039363534721254</v>
+        <v>2.023274487457062</v>
       </c>
     </row>
     <row r="23">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D23">
-        <v>1.551148335408239E-17</v>
+        <v>1.054515684429354E-17</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F23">
-        <v>-1.869447815147661</v>
+        <v>-1.83989478679631</v>
       </c>
       <c r="G23">
-        <v>1.856349357734679</v>
+        <v>1.948179197189389</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24">
-        <v>3.803085529577562E-17</v>
+        <v>2.909533972877171E-17</v>
       </c>
       <c r="E24">
         <v>0.9999999999999999</v>
       </c>
       <c r="F24">
-        <v>-3.053747979702225</v>
+        <v>-2.975516446991799</v>
       </c>
       <c r="G24">
-        <v>1.743187725338075</v>
+        <v>1.707625869684086</v>
       </c>
     </row>
     <row r="25">
@@ -1024,19 +1024,19 @@
         </is>
       </c>
       <c r="C25">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D25">
-        <v>-3.245275832313003E-17</v>
+        <v>-2.115149366832018E-16</v>
       </c>
       <c r="E25">
         <v>1</v>
       </c>
       <c r="F25">
-        <v>-1.363683774832632</v>
+        <v>-1.384237958324216</v>
       </c>
       <c r="G25">
-        <v>1.918854911631257</v>
+        <v>1.863854444457608</v>
       </c>
     </row>
     <row r="26">
@@ -1051,19 +1051,19 @@
         </is>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D26">
-        <v>2.460646112372784E-17</v>
+        <v>-2.314255351507749E-18</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>-2.064829789047005</v>
+        <v>-2.154663972431492</v>
       </c>
       <c r="G26">
-        <v>1.624233134082799</v>
+        <v>1.588926798804913</v>
       </c>
     </row>
     <row r="27">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27">
-        <v>-3.239017028862746E-16</v>
+        <v>-7.599560242012503E-16</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F27">
-        <v>-1.437006464188384</v>
+        <v>-1.397011270841194</v>
       </c>
       <c r="G27">
-        <v>2.361291707511</v>
+        <v>2.311255231028905</v>
       </c>
     </row>
     <row r="28">
@@ -1105,19 +1105,19 @@
         </is>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28">
-        <v>-1.143586882387551E-17</v>
+        <v>-2.173309069084634E-17</v>
       </c>
       <c r="E28">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>-1.013447046560743</v>
+        <v>-0.9748681252592677</v>
       </c>
       <c r="G28">
-        <v>2.267492478119101</v>
+        <v>2.238625731327224</v>
       </c>
     </row>
     <row r="29">
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C29">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29">
-        <v>2.057027212706589E-17</v>
+        <v>1.66244333114444E-18</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F29">
-        <v>-1.448603358368944</v>
+        <v>-1.450858431789388</v>
       </c>
       <c r="G29">
-        <v>2.174284104802546</v>
+        <v>2.112411861129588</v>
       </c>
     </row>
     <row r="30">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C30">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D30">
-        <v>5.079487178094588E-17</v>
+        <v>-3.330049529776907E-18</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>-1.813834765996075</v>
+        <v>-1.807781055024348</v>
       </c>
       <c r="G30">
-        <v>3.200105174907554</v>
+        <v>3.120417627981752</v>
       </c>
     </row>
     <row r="31">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="C31">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D31">
-        <v>2.855887086160681E-18</v>
+        <v>6.670941081278669E-17</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0.9999999999999999</v>
       </c>
       <c r="F31">
-        <v>-1.653423711067368</v>
+        <v>-1.696729378479287</v>
       </c>
       <c r="G31">
-        <v>1.745058586135704</v>
+        <v>1.697613823641754</v>
       </c>
     </row>
     <row r="32">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="C32">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32">
-        <v>9.903201207316459E-17</v>
+        <v>-7.006011181251569E-17</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>-1.450547055695796</v>
+        <v>-1.466755020657713</v>
       </c>
       <c r="G32">
-        <v>2.066485962284576</v>
+        <v>2.009011248205899</v>
       </c>
     </row>
     <row r="33">
@@ -1240,19 +1240,19 @@
         </is>
       </c>
       <c r="C33">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33">
-        <v>4.918396912125861E-17</v>
+        <v>1.454831522282186E-17</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33">
-        <v>-1.834671361908434</v>
+        <v>-1.842151580501379</v>
       </c>
       <c r="G33">
-        <v>1.96036784281024</v>
+        <v>1.956390195989459</v>
       </c>
     </row>
   </sheetData>
